--- a/dataset/construct/dataset_splits/data_size/10_percent/tum/fold1.xlsx
+++ b/dataset/construct/dataset_splits/data_size/10_percent/tum/fold1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,85 +625,85 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85.2467825500038</v>
+        <v>84.97033370725281</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>30.1109905115367</v>
       </c>
       <c r="E2" t="n">
-        <v>30.3460743801652</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="I2" t="n">
-        <v>3370</v>
+        <v>152</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>253</v>
       </c>
       <c r="K2" t="n">
-        <v>242.8</v>
+        <v>561</v>
       </c>
       <c r="L2" t="n">
-        <v>371.3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>285.3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>899.4</v>
+        <v>98</v>
       </c>
       <c r="O2" t="n">
-        <v>72.3</v>
+        <v>98</v>
       </c>
       <c r="P2" t="n">
-        <v>106.7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>85.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>264.3</v>
+        <v>96</v>
       </c>
       <c r="S2" t="n">
-        <v>22.6</v>
+        <v>96</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>53.2</v>
+        <v>24.3</v>
       </c>
       <c r="V2" t="n">
-        <v>75.8</v>
+        <v>0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X2" t="n">
-        <v>26.9</v>
+        <v>23.6114412754479</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.16382252559727</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.1836007130125</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>26.8217134966894</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -730,31 +715,24 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>566</v>
+        <v>612</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,40 +740,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>84.7733230663929</v>
+        <v>82.2897330595483</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="E3" t="n">
-        <v>20.829995193078</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="I3" t="n">
-        <v>1480</v>
+        <v>39.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>32.1</v>
       </c>
       <c r="K3" t="n">
-        <v>193</v>
+        <v>263.9</v>
       </c>
       <c r="L3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>283.8</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -813,34 +791,34 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>22.65</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X3" t="n">
-        <v>22.7</v>
+        <v>22.0244421422418</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.198412698412698</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.7909345556404</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.4508627838174</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -849,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -861,22 +839,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>104</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1094</v>
+        <v>1306</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,79 +855,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.44095254391971</v>
+        <v>86.2350005070094</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>21.6855368882395</v>
       </c>
       <c r="E4" t="n">
-        <v>25.3443526170798</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>10.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1550</v>
+        <v>136.9</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>420.7</v>
+        <v>220.2</v>
       </c>
       <c r="L4" t="n">
-        <v>199.2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>296.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>916.7</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>35.2</v>
+        <v>20.85</v>
       </c>
       <c r="V4" t="n">
-        <v>35.2</v>
+        <v>0.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>20.912910618793</v>
       </c>
       <c r="X4" t="n">
-        <v>23.25</v>
+        <v>20.4698827870943</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.204633204633205</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.3002291825821</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>22.8943655965997</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
@@ -971,36 +942,27 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2031</v>
+        <v>624</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,79 +970,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>85.6764691865034</v>
+        <v>90.1065803483155</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>20.0288415318058</v>
       </c>
       <c r="E5" t="n">
-        <v>27.7777777777777</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I5" t="n">
-        <v>882</v>
+        <v>45</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K5" t="n">
-        <v>423.4</v>
+        <v>156</v>
       </c>
       <c r="L5" t="n">
-        <v>142.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>389.7</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>955.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>55.1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>29.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>198.5</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>65.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>27.2</v>
+        <v>22.15</v>
       </c>
       <c r="V5" t="n">
-        <v>92.59999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X5" t="n">
-        <v>28.85</v>
+        <v>21.9926337013585</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.235474006116208</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.4435956200662</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>28.5191036537487</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1107,22 +1069,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>208</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>551</v>
+        <v>2012</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1130,88 +1085,88 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>86.878606738155</v>
+        <v>84.8005503270211</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>25.5102040816326</v>
       </c>
       <c r="E6" t="n">
-        <v>23.1481481481481</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>564.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1010</v>
+        <v>316.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>120.3</v>
       </c>
       <c r="K6" t="n">
-        <v>852</v>
+        <v>1001.9</v>
       </c>
       <c r="L6" t="n">
-        <v>377</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>892</v>
+        <v>6.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2121</v>
+        <v>15.3</v>
       </c>
       <c r="O6" t="n">
-        <v>300</v>
+        <v>116.3</v>
       </c>
       <c r="P6" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>204</v>
+        <v>24.85</v>
       </c>
       <c r="V6" t="n">
-        <v>474</v>
+        <v>0.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>25.9103641456583</v>
       </c>
       <c r="X6" t="n">
-        <v>23.7</v>
+        <v>24.8126692377086</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.197718631178707</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>23.5033791921504</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1220,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1229,24 +1184,15 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>76</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>234</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>914</v>
+        <v>1427</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1254,79 +1200,79 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84.0671732958146</v>
+        <v>86.99098473901689</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>25.2080856123662</v>
       </c>
       <c r="E7" t="n">
-        <v>25.7629805786761</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>319.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1400</v>
+        <v>203</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>264.3</v>
       </c>
       <c r="K7" t="n">
-        <v>855</v>
+        <v>786.8</v>
       </c>
       <c r="L7" t="n">
-        <v>534</v>
+        <v>36.6</v>
       </c>
       <c r="M7" t="n">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1817</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>50</v>
+        <v>36.6</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>93</v>
+        <v>22.35</v>
       </c>
       <c r="V7" t="n">
-        <v>93</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>23.0137509549274</v>
       </c>
       <c r="X7" t="n">
-        <v>29</v>
+        <v>22.1512191514658</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.220858895705522</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>29.921059332824</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>29.2679951700071</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1347,24 +1293,17 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
         <v>154</v>
       </c>
-      <c r="AN7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
